--- a/results_v3/tables/table4_mcts_ablation.xlsx
+++ b/results_v3/tables/table4_mcts_ablation.xlsx
@@ -539,7 +539,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.65±0.07</t>
+          <t>0.68±0.04</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.55±0.17</t>
+          <t>0.68±0.04</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">

--- a/results_v3/tables/table4_mcts_ablation.xlsx
+++ b/results_v3/tables/table4_mcts_ablation.xlsx
@@ -441,22 +441,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MuZero (M=50, D=5)</t>
+          <t>MuZero (M=100, D=5)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.64±0.08</t>
+          <t>0.72±0.08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.57±0.15</t>
+          <t>0.68±0.04</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.14±0.05</t>
+          <t>0.28±0.06</t>
         </is>
       </c>
     </row>
